--- a/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 4,71</t>
+          <t>-41,36; 5,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,79</t>
+          <t>-2,3; 0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,7</t>
+          <t>-1,48; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 0,18</t>
+          <t>-26,11; 0,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,17</t>
+          <t>-0,67; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,24</t>
+          <t>-1,76; 1,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,33</t>
+          <t>-0,72; 2,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,54</t>
+          <t>-4,74; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 778,86</t>
+          <t>-62,94; 586,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 216,51</t>
+          <t>-77,11; 241,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 731,31</t>
+          <t>-66,48; 706,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,44</t>
+          <t>-0,31; 3,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,55</t>
+          <t>-0,81; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,13</t>
+          <t>-2,91; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 4,85</t>
+          <t>-10,24; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,39; 154,42</t>
+          <t>-88,11; 167,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 85,23</t>
+          <t>-66,84; 109,37</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,55</t>
+          <t>0,94; 6,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,48</t>
+          <t>-5,15; 0,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 2,29</t>
+          <t>-19,44; 1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 24,12</t>
+          <t>-75,27; 24,31</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,31</t>
+          <t>-1,84; 0,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,44</t>
+          <t>-2,0; 0,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,44</t>
+          <t>-0,08; 2,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 3,46</t>
+          <t>-33,62; 2,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-94,69; 27,76</t>
+          <t>-95,18; 28,98</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,68</t>
+          <t>-1,21; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,6</t>
+          <t>-0,26; 2,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,69</t>
+          <t>-0,95; 2,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 8,63</t>
+          <t>-11,12; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 21,55</t>
+          <t>-20,52; 21,84</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,8</t>
+          <t>-0,39; 0,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,97</t>
+          <t>-0,25; 1,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,64</t>
+          <t>-0,59; 0,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 1,72</t>
+          <t>-11,4; 2,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 243,11</t>
+          <t>-49,16; 212,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 187,9</t>
+          <t>-28,45; 193,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 101,51</t>
+          <t>-48,05; 98,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 10,82</t>
+          <t>-58,91; 17,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-12,28</t>
+          <t>-10,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-71,9%</t>
+          <t>-75,6%</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 5,75</t>
+          <t>-35,12; 3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,06</t>
+          <t>-4,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-97,28%</t>
+          <t>-77,73%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,78</t>
+          <t>-2,22; 0,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,67</t>
+          <t>-1,24; 1,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 0,34</t>
+          <t>-24,33; 2,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-42,16%</t>
+          <t>-30,1%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,09</t>
+          <t>-0,66; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,26</t>
+          <t>-1,55; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,25</t>
+          <t>-0,69; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,69</t>
+          <t>-3,42; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 586,42</t>
+          <t>-62,83; 632,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 241,78</t>
+          <t>-76,11; 313,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 706,62</t>
+          <t>-61,6; 802,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-23,53%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,69</t>
+          <t>-0,32; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,55</t>
+          <t>-1,02; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,37</t>
+          <t>-2,96; 1,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 4,71</t>
+          <t>-8,98; 5,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1000,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 167,93</t>
+          <t>-88,35; 122,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,84; 109,37</t>
+          <t>-60,67; 122,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,13</t>
+          <t>-7,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-44,26%</t>
+          <t>-43,64%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,21</t>
+          <t>1,36; 5,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 0,47</t>
+          <t>-4,41; 0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 1,84</t>
+          <t>-18,6; 1,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,27; 24,31</t>
+          <t>-74,53; 15,37</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-16,4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-74,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,57</t>
+          <t>-2,14; 0,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,47</t>
+          <t>-1,75; 0,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,44</t>
+          <t>-0,07; 2,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 2,79</t>
+          <t>-11,69; 12,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,18; 28,98</t>
+          <t>-37,95; 76,74</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,68</t>
+          <t>-1,18; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,57</t>
+          <t>-0,4; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,0</t>
+          <t>-0,95; 2,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 8,91</t>
+          <t>-10,57; 9,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 21,84</t>
+          <t>-20,26; 24,35</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-19,32%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,73</t>
+          <t>-0,37; 0,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,0</t>
+          <t>-0,19; 1,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,59</t>
+          <t>-0,6; 0,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 2,5</t>
+          <t>-2,38; 4,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 212,0</t>
+          <t>-45,44; 216,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 193,1</t>
+          <t>-20,16; 185,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 98,26</t>
+          <t>-47,68; 98,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 17,21</t>
+          <t>-13,23; 37,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
